--- a/HVWBusSet.xlsx
+++ b/HVWBusSet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/319a91e8a51c869d/Dokumentumok/GitHub/HVW-Bus-Set/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{4FD17092-67A2-4D4C-9A13-270539237338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B041574-462C-42F7-A502-9A4983F3C3C6}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{4FD17092-67A2-4D4C-9A13-270539237338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BF9883B-77F4-4425-B741-36D631DD4B36}"/>
   <bookViews>
-    <workbookView xWindow="408" yWindow="384" windowWidth="30588" windowHeight="24384" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14712" yWindow="840" windowWidth="30588" windowHeight="24384" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="V4.0" sheetId="11" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3466" uniqueCount="266">
   <si>
     <t>ID</t>
   </si>
@@ -703,12 +703,6 @@
     <t>Switzerland</t>
   </si>
   <si>
-    <t>1CC</t>
-  </si>
-  <si>
-    <t>2CC</t>
-  </si>
-  <si>
     <t>Europe</t>
   </si>
   <si>
@@ -818,6 +812,33 @@
   </si>
   <si>
     <t>....,xx</t>
+  </si>
+  <si>
+    <t>Volvo 7700</t>
+  </si>
+  <si>
+    <t>Alfa Civis 12</t>
+  </si>
+  <si>
+    <t>Alfa Localo</t>
+  </si>
+  <si>
+    <t>Alfa Regio</t>
+  </si>
+  <si>
+    <t>BKV_CC</t>
+  </si>
+  <si>
+    <t>Volvo 7700A</t>
+  </si>
+  <si>
+    <t>Volvo 7700 FL</t>
+  </si>
+  <si>
+    <t>Volvo 7700 FL Hybrid</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -1584,16 +1605,16 @@
         <v>121</v>
       </c>
       <c r="AN1" s="30" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AO1" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AP1" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="AQ1" s="2" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:43">
@@ -1673,7 +1694,7 @@
         <v>206</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK2" t="s">
         <v>95</v>
@@ -1685,7 +1706,7 @@
         <v>3000</v>
       </c>
       <c r="AN2" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO2">
         <v>30</v>
@@ -1774,7 +1795,7 @@
         <v>206</v>
       </c>
       <c r="AJ3" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK3" t="s">
         <v>95</v>
@@ -1786,7 +1807,7 @@
         <v>3000.01</v>
       </c>
       <c r="AN3" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO3">
         <v>30</v>
@@ -1875,7 +1896,7 @@
         <v>206</v>
       </c>
       <c r="AJ4" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK4" t="s">
         <v>95</v>
@@ -1887,7 +1908,7 @@
         <v>3000.02</v>
       </c>
       <c r="AN4" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO4">
         <v>30</v>
@@ -1901,7 +1922,7 @@
     </row>
     <row r="5" spans="1:43">
       <c r="A5" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B5">
         <v>9.5</v>
@@ -1913,7 +1934,7 @@
         <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G5" s="5">
         <v>2000</v>
@@ -1976,16 +1997,16 @@
         <v>215</v>
       </c>
       <c r="AG5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AH5" s="1">
         <v>9.5</v>
       </c>
       <c r="AJ5" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL5" t="s">
         <v>101</v>
@@ -1994,7 +2015,7 @@
         <v>4000</v>
       </c>
       <c r="AN5" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO5">
         <v>40</v>
@@ -2008,7 +2029,7 @@
     </row>
     <row r="6" spans="1:43">
       <c r="A6" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B6">
         <v>11</v>
@@ -2020,7 +2041,7 @@
         <v>87</v>
       </c>
       <c r="F6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G6" s="5">
         <v>2002</v>
@@ -2083,16 +2104,16 @@
         <v>215</v>
       </c>
       <c r="AG6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AH6" s="1">
         <v>11</v>
       </c>
       <c r="AJ6" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL6" t="s">
         <v>101</v>
@@ -2101,7 +2122,7 @@
         <v>4001</v>
       </c>
       <c r="AN6" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO6">
         <v>40</v>
@@ -2193,7 +2214,7 @@
         <v>10</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK7" t="s">
         <v>96</v>
@@ -2205,7 +2226,7 @@
         <v>4007</v>
       </c>
       <c r="AN7" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO7">
         <v>40</v>
@@ -2300,7 +2321,7 @@
         <v>208</v>
       </c>
       <c r="AJ8" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK8" t="s">
         <v>95</v>
@@ -2312,7 +2333,7 @@
         <v>4008</v>
       </c>
       <c r="AN8" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO8">
         <v>40</v>
@@ -2404,7 +2425,7 @@
         <v>12</v>
       </c>
       <c r="AJ9" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK9" t="s">
         <v>95</v>
@@ -2416,7 +2437,7 @@
         <v>4009</v>
       </c>
       <c r="AN9" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO9">
         <v>40</v>
@@ -2511,7 +2532,7 @@
         <v>209</v>
       </c>
       <c r="AJ10" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK10" t="s">
         <v>119</v>
@@ -2523,7 +2544,7 @@
         <v>4010</v>
       </c>
       <c r="AN10" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO10">
         <v>40</v>
@@ -2615,7 +2636,7 @@
         <v>13</v>
       </c>
       <c r="AJ11" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK11" t="s">
         <v>119</v>
@@ -2627,7 +2648,7 @@
         <v>4011</v>
       </c>
       <c r="AN11" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO11">
         <v>40</v>
@@ -2641,7 +2662,7 @@
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B12">
         <v>9.5</v>
@@ -2653,7 +2674,7 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G12" s="5">
         <v>2000</v>
@@ -2713,16 +2734,16 @@
         <v>215</v>
       </c>
       <c r="AG12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AH12" s="1">
         <v>9.5</v>
       </c>
       <c r="AJ12" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL12" t="s">
         <v>120</v>
@@ -2731,7 +2752,7 @@
         <v>4014</v>
       </c>
       <c r="AN12" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO12">
         <v>40</v>
@@ -2745,7 +2766,7 @@
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B13">
         <v>11</v>
@@ -2757,7 +2778,7 @@
         <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G13" s="5">
         <v>2003</v>
@@ -2817,16 +2838,16 @@
         <v>215</v>
       </c>
       <c r="AG13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AH13" s="1">
         <v>11</v>
       </c>
       <c r="AJ13" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL13" t="s">
         <v>120</v>
@@ -2835,7 +2856,7 @@
         <v>4015</v>
       </c>
       <c r="AN13" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO13">
         <v>40</v>
@@ -2849,7 +2870,7 @@
     </row>
     <row r="14" spans="1:43">
       <c r="A14" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B14">
         <v>12</v>
@@ -2861,7 +2882,7 @@
         <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G14" s="5">
         <v>2004</v>
@@ -2921,13 +2942,13 @@
         <v>215</v>
       </c>
       <c r="AG14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AH14" s="1">
         <v>12</v>
       </c>
       <c r="AJ14" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK14" t="s">
         <v>95</v>
@@ -2939,7 +2960,7 @@
         <v>4016</v>
       </c>
       <c r="AN14" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO14">
         <v>40</v>
@@ -3031,7 +3052,7 @@
         <v>204</v>
       </c>
       <c r="AJ15" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK15" t="s">
         <v>95</v>
@@ -3043,7 +3064,7 @@
         <v>4017</v>
       </c>
       <c r="AN15" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO15">
         <v>40</v>
@@ -3057,7 +3078,7 @@
     </row>
     <row r="16" spans="1:43">
       <c r="A16" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B16">
         <v>9.5</v>
@@ -3069,7 +3090,7 @@
         <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G16" s="5">
         <v>2000</v>
@@ -3129,25 +3150,25 @@
         <v>215</v>
       </c>
       <c r="AG16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AH16" s="1">
         <v>9.5</v>
       </c>
       <c r="AJ16" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM16" s="9">
         <v>4018</v>
       </c>
       <c r="AN16" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO16">
         <v>40</v>
@@ -3161,7 +3182,7 @@
     </row>
     <row r="17" spans="1:43">
       <c r="A17" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B17">
         <v>11</v>
@@ -3173,7 +3194,7 @@
         <v>87</v>
       </c>
       <c r="F17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G17" s="5">
         <v>2001</v>
@@ -3233,25 +3254,25 @@
         <v>215</v>
       </c>
       <c r="AG17" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AH17" s="1">
         <v>11</v>
       </c>
       <c r="AJ17" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK17" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL17" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM17" s="9">
         <v>4019</v>
       </c>
       <c r="AN17" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO17">
         <v>40</v>
@@ -3265,7 +3286,7 @@
     </row>
     <row r="18" spans="1:43">
       <c r="A18" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B18">
         <v>12</v>
@@ -3277,7 +3298,7 @@
         <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G18" s="5">
         <v>2005</v>
@@ -3337,25 +3358,25 @@
         <v>215</v>
       </c>
       <c r="AG18" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AH18" s="1">
         <v>12</v>
       </c>
       <c r="AJ18" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK18" t="s">
         <v>95</v>
       </c>
       <c r="AL18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM18" s="9">
         <v>4020</v>
       </c>
       <c r="AN18" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO18">
         <v>40</v>
@@ -3447,19 +3468,19 @@
         <v>205</v>
       </c>
       <c r="AJ19" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK19" t="s">
         <v>95</v>
       </c>
       <c r="AL19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM19" s="9">
         <v>4021</v>
       </c>
       <c r="AN19" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO19">
         <v>40</v>
@@ -3473,10 +3494,10 @@
     </row>
     <row r="20" spans="1:43">
       <c r="A20" s="28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -3485,7 +3506,7 @@
         <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G20" s="5">
         <v>2005</v>
@@ -3545,25 +3566,25 @@
         <v>215</v>
       </c>
       <c r="AG20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AH20" s="1">
         <v>9.5</v>
       </c>
       <c r="AJ20" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK20" t="s">
+        <v>243</v>
+      </c>
+      <c r="AL20" t="s">
         <v>245</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>247</v>
       </c>
       <c r="AM20" s="9">
         <v>4022</v>
       </c>
       <c r="AN20" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO20">
         <v>40</v>
@@ -3577,10 +3598,10 @@
     </row>
     <row r="21" spans="1:43">
       <c r="A21" s="28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -3589,7 +3610,7 @@
         <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G21" s="5">
         <v>2003</v>
@@ -3649,25 +3670,25 @@
         <v>215</v>
       </c>
       <c r="AG21" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AH21" s="1">
         <v>11</v>
       </c>
       <c r="AJ21" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK21" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM21" s="9">
         <v>4023</v>
       </c>
       <c r="AN21" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO21">
         <v>40</v>
@@ -3681,7 +3702,7 @@
     </row>
     <row r="22" spans="1:43">
       <c r="A22" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B22">
         <v>12</v>
@@ -3693,7 +3714,7 @@
         <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G22" s="5">
         <v>2008</v>
@@ -3753,25 +3774,25 @@
         <v>215</v>
       </c>
       <c r="AG22" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AH22" s="1">
         <v>12</v>
       </c>
       <c r="AJ22" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK22" t="s">
         <v>95</v>
       </c>
       <c r="AL22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM22" s="9">
         <v>4024</v>
       </c>
       <c r="AN22" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO22">
         <v>40</v>
@@ -3863,19 +3884,19 @@
         <v>10</v>
       </c>
       <c r="AJ23" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK23" t="s">
         <v>96</v>
       </c>
       <c r="AL23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM23" s="9">
         <v>4025</v>
       </c>
       <c r="AN23" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO23">
         <v>40</v>
@@ -3967,19 +3988,19 @@
         <v>12</v>
       </c>
       <c r="AJ24" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK24" t="s">
         <v>95</v>
       </c>
       <c r="AL24" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM24" s="9">
         <v>4026</v>
       </c>
       <c r="AN24" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO24">
         <v>40</v>
@@ -4077,7 +4098,7 @@
         <v>150</v>
       </c>
       <c r="AJ25" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK25" t="s">
         <v>96</v>
@@ -4089,7 +4110,7 @@
         <v>5500</v>
       </c>
       <c r="AN25" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO25">
         <v>55</v>
@@ -4187,7 +4208,7 @@
         <v>150</v>
       </c>
       <c r="AJ26" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK26" t="s">
         <v>96</v>
@@ -4199,7 +4220,7 @@
         <v>5500.01</v>
       </c>
       <c r="AN26" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO26">
         <v>55</v>
@@ -4297,7 +4318,7 @@
         <v>150</v>
       </c>
       <c r="AJ27" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK27" t="s">
         <v>96</v>
@@ -4407,7 +4428,7 @@
         <v>150</v>
       </c>
       <c r="AJ28" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK28" t="s">
         <v>96</v>
@@ -4419,7 +4440,7 @@
         <v>5500.03</v>
       </c>
       <c r="AN28" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AO28">
         <v>55</v>
@@ -4514,7 +4535,7 @@
         <v>150</v>
       </c>
       <c r="AJ29" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK29" t="s">
         <v>96</v>
@@ -4526,7 +4547,7 @@
         <v>5501</v>
       </c>
       <c r="AN29" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO29">
         <v>55</v>
@@ -4621,7 +4642,7 @@
         <v>150</v>
       </c>
       <c r="AJ30" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK30" t="s">
         <v>96</v>
@@ -4633,7 +4654,7 @@
         <v>5501.01</v>
       </c>
       <c r="AN30" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO30">
         <v>55</v>
@@ -4728,7 +4749,7 @@
         <v>150</v>
       </c>
       <c r="AJ31" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK31" t="s">
         <v>96</v>
@@ -4838,7 +4859,7 @@
         <v>151</v>
       </c>
       <c r="AJ32" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK32" t="s">
         <v>95</v>
@@ -4850,7 +4871,7 @@
         <v>5502</v>
       </c>
       <c r="AN32" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO32">
         <v>55</v>
@@ -4948,7 +4969,7 @@
         <v>151</v>
       </c>
       <c r="AJ33" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK33" t="s">
         <v>95</v>
@@ -4960,7 +4981,7 @@
         <v>5502.01</v>
       </c>
       <c r="AN33" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO33">
         <v>55</v>
@@ -5058,7 +5079,7 @@
         <v>152</v>
       </c>
       <c r="AJ34" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK34" t="s">
         <v>95</v>
@@ -5070,7 +5091,7 @@
         <v>5503</v>
       </c>
       <c r="AN34" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO34">
         <v>55</v>
@@ -5168,7 +5189,7 @@
         <v>152</v>
       </c>
       <c r="AJ35" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK35" t="s">
         <v>95</v>
@@ -5180,7 +5201,7 @@
         <v>5503.01</v>
       </c>
       <c r="AN35" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO35">
         <v>55</v>
@@ -5278,7 +5299,7 @@
         <v>153</v>
       </c>
       <c r="AJ36" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK36" t="s">
         <v>95</v>
@@ -5290,7 +5311,7 @@
         <v>5504</v>
       </c>
       <c r="AN36" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO36">
         <v>55</v>
@@ -5388,7 +5409,7 @@
         <v>153</v>
       </c>
       <c r="AJ37" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK37" t="s">
         <v>95</v>
@@ -5400,7 +5421,7 @@
         <v>5504.01</v>
       </c>
       <c r="AN37" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO37">
         <v>55</v>
@@ -5495,7 +5516,7 @@
         <v>151</v>
       </c>
       <c r="AJ38" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK38" t="s">
         <v>95</v>
@@ -5507,7 +5528,7 @@
         <v>5505</v>
       </c>
       <c r="AN38" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO38">
         <v>55</v>
@@ -5602,7 +5623,7 @@
         <v>151</v>
       </c>
       <c r="AJ39" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK39" t="s">
         <v>95</v>
@@ -5614,7 +5635,7 @@
         <v>5505.01</v>
       </c>
       <c r="AN39" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO39">
         <v>55</v>
@@ -5709,7 +5730,7 @@
         <v>152</v>
       </c>
       <c r="AJ40" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK40" t="s">
         <v>95</v>
@@ -5721,7 +5742,7 @@
         <v>5506</v>
       </c>
       <c r="AN40" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO40">
         <v>55</v>
@@ -5816,7 +5837,7 @@
         <v>152</v>
       </c>
       <c r="AJ41" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK41" t="s">
         <v>95</v>
@@ -5828,7 +5849,7 @@
         <v>5506.01</v>
       </c>
       <c r="AN41" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO41">
         <v>55</v>
@@ -5923,7 +5944,7 @@
         <v>153</v>
       </c>
       <c r="AJ42" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK42" t="s">
         <v>95</v>
@@ -5935,7 +5956,7 @@
         <v>5507</v>
       </c>
       <c r="AN42" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO42">
         <v>55</v>
@@ -6030,7 +6051,7 @@
         <v>153</v>
       </c>
       <c r="AJ43" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK43" t="s">
         <v>95</v>
@@ -6042,7 +6063,7 @@
         <v>5507.01</v>
       </c>
       <c r="AN43" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO43">
         <v>55</v>
@@ -6149,7 +6170,7 @@
         <v>154</v>
       </c>
       <c r="AJ44" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK44" t="s">
         <v>116</v>
@@ -6161,7 +6182,7 @@
         <v>5508</v>
       </c>
       <c r="AN44" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO44">
         <v>55</v>
@@ -6268,7 +6289,7 @@
         <v>154</v>
       </c>
       <c r="AJ45" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK45" t="s">
         <v>116</v>
@@ -6280,7 +6301,7 @@
         <v>5508.01</v>
       </c>
       <c r="AN45" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO45">
         <v>55</v>
@@ -6387,7 +6408,7 @@
         <v>155</v>
       </c>
       <c r="AJ46" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK46" t="s">
         <v>116</v>
@@ -6399,7 +6420,7 @@
         <v>5509</v>
       </c>
       <c r="AN46" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO46">
         <v>55</v>
@@ -6506,7 +6527,7 @@
         <v>155</v>
       </c>
       <c r="AJ47" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK47" t="s">
         <v>116</v>
@@ -6518,7 +6539,7 @@
         <v>5509.01</v>
       </c>
       <c r="AN47" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO47">
         <v>55</v>
@@ -6625,7 +6646,7 @@
         <v>156</v>
       </c>
       <c r="AJ48" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK48" t="s">
         <v>116</v>
@@ -6637,7 +6658,7 @@
         <v>5510</v>
       </c>
       <c r="AN48" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO48">
         <v>55</v>
@@ -6744,7 +6765,7 @@
         <v>156</v>
       </c>
       <c r="AJ49" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK49" t="s">
         <v>116</v>
@@ -6756,7 +6777,7 @@
         <v>5510.01</v>
       </c>
       <c r="AN49" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO49">
         <v>55</v>
@@ -6860,7 +6881,7 @@
         <v>154</v>
       </c>
       <c r="AJ50" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK50" t="s">
         <v>116</v>
@@ -6872,7 +6893,7 @@
         <v>5511</v>
       </c>
       <c r="AN50" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO50">
         <v>55</v>
@@ -6976,7 +6997,7 @@
         <v>154</v>
       </c>
       <c r="AJ51" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK51" t="s">
         <v>116</v>
@@ -6988,7 +7009,7 @@
         <v>5511.01</v>
       </c>
       <c r="AN51" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO51">
         <v>55</v>
@@ -7092,7 +7113,7 @@
         <v>155</v>
       </c>
       <c r="AJ52" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK52" t="s">
         <v>116</v>
@@ -7104,7 +7125,7 @@
         <v>5512</v>
       </c>
       <c r="AN52" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO52">
         <v>55</v>
@@ -7208,7 +7229,7 @@
         <v>155</v>
       </c>
       <c r="AJ53" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK53" t="s">
         <v>116</v>
@@ -7220,7 +7241,7 @@
         <v>5512.01</v>
       </c>
       <c r="AN53" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO53">
         <v>55</v>
@@ -7324,7 +7345,7 @@
         <v>156</v>
       </c>
       <c r="AJ54" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK54" t="s">
         <v>116</v>
@@ -7336,7 +7357,7 @@
         <v>5513</v>
       </c>
       <c r="AN54" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO54">
         <v>55</v>
@@ -7440,7 +7461,7 @@
         <v>156</v>
       </c>
       <c r="AJ55" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK55" t="s">
         <v>116</v>
@@ -7452,7 +7473,7 @@
         <v>5513.01</v>
       </c>
       <c r="AN55" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO55">
         <v>55</v>
@@ -7547,7 +7568,7 @@
         <v>187</v>
       </c>
       <c r="AJ56" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK56" t="s">
         <v>95</v>
@@ -7559,7 +7580,7 @@
         <v>5620</v>
       </c>
       <c r="AN56" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO56">
         <v>56</v>
@@ -7654,7 +7675,7 @@
         <v>191</v>
       </c>
       <c r="AJ57" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK57" t="s">
         <v>119</v>
@@ -7666,7 +7687,7 @@
         <v>5621</v>
       </c>
       <c r="AN57" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO57">
         <v>56</v>
@@ -7764,7 +7785,7 @@
         <v>192</v>
       </c>
       <c r="AJ58" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK58" t="s">
         <v>190</v>
@@ -7776,7 +7797,7 @@
         <v>5622</v>
       </c>
       <c r="AN58" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO58">
         <v>56</v>
@@ -7871,7 +7892,7 @@
         <v>186</v>
       </c>
       <c r="AJ59" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK59" t="s">
         <v>95</v>
@@ -7883,7 +7904,7 @@
         <v>5720</v>
       </c>
       <c r="AN59" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO59">
         <v>57</v>
@@ -7978,7 +7999,7 @@
         <v>188</v>
       </c>
       <c r="AJ60" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK60" t="s">
         <v>119</v>
@@ -7990,7 +8011,7 @@
         <v>5721</v>
       </c>
       <c r="AN60" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO60">
         <v>57</v>
@@ -8085,7 +8106,7 @@
         <v>188</v>
       </c>
       <c r="AJ61" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK61" t="s">
         <v>119</v>
@@ -8097,7 +8118,7 @@
         <v>5721.01</v>
       </c>
       <c r="AN61" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO61">
         <v>57</v>
@@ -8171,7 +8192,7 @@
         <v>160</v>
       </c>
       <c r="Y62" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Z62" s="5">
         <v>8</v>
@@ -8192,7 +8213,7 @@
         <v>188</v>
       </c>
       <c r="AJ62" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK62" t="s">
         <v>119</v>
@@ -8204,7 +8225,7 @@
         <v>5721.02</v>
       </c>
       <c r="AN62" s="29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AO62">
         <v>57</v>
@@ -8302,7 +8323,7 @@
         <v>189</v>
       </c>
       <c r="AJ63" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK63" t="s">
         <v>190</v>
@@ -8314,7 +8335,7 @@
         <v>5722</v>
       </c>
       <c r="AN63" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO63">
         <v>57</v>
@@ -8409,7 +8430,7 @@
         <v>2</v>
       </c>
       <c r="AJ64" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK64" t="s">
         <v>95</v>
@@ -8421,7 +8442,7 @@
         <v>6500</v>
       </c>
       <c r="AN64" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO64">
         <v>65</v>
@@ -8516,7 +8537,7 @@
         <v>2</v>
       </c>
       <c r="AJ65" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK65" t="s">
         <v>95</v>
@@ -8528,7 +8549,7 @@
         <v>6500.01</v>
       </c>
       <c r="AN65" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO65">
         <v>65</v>
@@ -8635,7 +8656,7 @@
         <v>108</v>
       </c>
       <c r="AJ66" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK66" t="s">
         <v>116</v>
@@ -8647,7 +8668,7 @@
         <v>6502</v>
       </c>
       <c r="AN66" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO66">
         <v>65</v>
@@ -8754,7 +8775,7 @@
         <v>108</v>
       </c>
       <c r="AJ67" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK67" t="s">
         <v>116</v>
@@ -8766,7 +8787,7 @@
         <v>6502.01</v>
       </c>
       <c r="AN67" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO67">
         <v>65</v>
@@ -8864,7 +8885,7 @@
         <v>92</v>
       </c>
       <c r="AJ68" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK68" t="s">
         <v>96</v>
@@ -8876,7 +8897,7 @@
         <v>6504</v>
       </c>
       <c r="AN68" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO68">
         <v>65</v>
@@ -8974,7 +8995,7 @@
         <v>92</v>
       </c>
       <c r="AJ69" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK69" t="s">
         <v>96</v>
@@ -8986,7 +9007,7 @@
         <v>6504.01</v>
       </c>
       <c r="AN69" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO69">
         <v>65</v>
@@ -9084,7 +9105,7 @@
         <v>92</v>
       </c>
       <c r="AJ70" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK70" t="s">
         <v>96</v>
@@ -9194,7 +9215,7 @@
         <v>92</v>
       </c>
       <c r="AJ71" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK71" t="s">
         <v>96</v>
@@ -9206,7 +9227,7 @@
         <v>6505</v>
       </c>
       <c r="AN71" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO71">
         <v>65</v>
@@ -9304,7 +9325,7 @@
         <v>92</v>
       </c>
       <c r="AJ72" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK72" t="s">
         <v>96</v>
@@ -9316,7 +9337,7 @@
         <v>6505.01</v>
       </c>
       <c r="AN72" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO72">
         <v>65</v>
@@ -9411,7 +9432,7 @@
         <v>92</v>
       </c>
       <c r="AJ73" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK73" t="s">
         <v>96</v>
@@ -9423,7 +9444,7 @@
         <v>6506</v>
       </c>
       <c r="AN73" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO73">
         <v>65</v>
@@ -9518,7 +9539,7 @@
         <v>92</v>
       </c>
       <c r="AJ74" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK74" t="s">
         <v>96</v>
@@ -9530,7 +9551,7 @@
         <v>6506.01</v>
       </c>
       <c r="AN74" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO74">
         <v>65</v>
@@ -9625,7 +9646,7 @@
         <v>92</v>
       </c>
       <c r="AJ75" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK75" t="s">
         <v>96</v>
@@ -9637,7 +9658,7 @@
         <v>6507</v>
       </c>
       <c r="AN75" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO75">
         <v>65</v>
@@ -9732,7 +9753,7 @@
         <v>92</v>
       </c>
       <c r="AJ76" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK76" t="s">
         <v>96</v>
@@ -9744,7 +9765,7 @@
         <v>6507.01</v>
       </c>
       <c r="AN76" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO76">
         <v>65</v>
@@ -9839,7 +9860,7 @@
         <v>91</v>
       </c>
       <c r="AJ77" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK77" t="s">
         <v>95</v>
@@ -9851,7 +9872,7 @@
         <v>6508</v>
       </c>
       <c r="AN77" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO77">
         <v>65</v>
@@ -9946,7 +9967,7 @@
         <v>91</v>
       </c>
       <c r="AJ78" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK78" t="s">
         <v>95</v>
@@ -9958,7 +9979,7 @@
         <v>6508.01</v>
       </c>
       <c r="AN78" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO78">
         <v>65</v>
@@ -10053,7 +10074,7 @@
         <v>91</v>
       </c>
       <c r="AJ79" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK79" t="s">
         <v>95</v>
@@ -10160,7 +10181,7 @@
         <v>91</v>
       </c>
       <c r="AJ80" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK80" t="s">
         <v>95</v>
@@ -10267,7 +10288,7 @@
         <v>91</v>
       </c>
       <c r="AJ81" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK81" t="s">
         <v>95</v>
@@ -10374,7 +10395,7 @@
         <v>91</v>
       </c>
       <c r="AJ82" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK82" t="s">
         <v>95</v>
@@ -10481,7 +10502,7 @@
         <v>91</v>
       </c>
       <c r="AJ83" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK83" t="s">
         <v>95</v>
@@ -10493,7 +10514,7 @@
         <v>6509</v>
       </c>
       <c r="AN83" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO83">
         <v>65</v>
@@ -10588,7 +10609,7 @@
         <v>91</v>
       </c>
       <c r="AJ84" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK84" t="s">
         <v>95</v>
@@ -10600,7 +10621,7 @@
         <v>6509.01</v>
       </c>
       <c r="AN84" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO84">
         <v>65</v>
@@ -10695,7 +10716,7 @@
         <v>91</v>
       </c>
       <c r="AJ85" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK85" t="s">
         <v>95</v>
@@ -10707,7 +10728,7 @@
         <v>6510</v>
       </c>
       <c r="AN85" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO85">
         <v>65</v>
@@ -10802,7 +10823,7 @@
         <v>91</v>
       </c>
       <c r="AJ86" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK86" t="s">
         <v>95</v>
@@ -10814,7 +10835,7 @@
         <v>6510.01</v>
       </c>
       <c r="AN86" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO86">
         <v>65</v>
@@ -10909,7 +10930,7 @@
         <v>91</v>
       </c>
       <c r="AJ87" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK87" t="s">
         <v>95</v>
@@ -11016,7 +11037,7 @@
         <v>91</v>
       </c>
       <c r="AJ88" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK88" t="s">
         <v>95</v>
@@ -11123,7 +11144,7 @@
         <v>91</v>
       </c>
       <c r="AJ89" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK89" t="s">
         <v>95</v>
@@ -11230,7 +11251,7 @@
         <v>91</v>
       </c>
       <c r="AJ90" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK90" t="s">
         <v>95</v>
@@ -11337,7 +11358,7 @@
         <v>91</v>
       </c>
       <c r="AJ91" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK91" t="s">
         <v>95</v>
@@ -11444,7 +11465,7 @@
         <v>91</v>
       </c>
       <c r="AJ92" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK92" t="s">
         <v>95</v>
@@ -11551,7 +11572,7 @@
         <v>91</v>
       </c>
       <c r="AJ93" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK93" t="s">
         <v>95</v>
@@ -11658,7 +11679,7 @@
         <v>91</v>
       </c>
       <c r="AJ94" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK94" t="s">
         <v>95</v>
@@ -11765,7 +11786,7 @@
         <v>91</v>
       </c>
       <c r="AJ95" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK95" t="s">
         <v>95</v>
@@ -11872,7 +11893,7 @@
         <v>91</v>
       </c>
       <c r="AJ96" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK96" t="s">
         <v>95</v>
@@ -11976,7 +11997,7 @@
         <v>91</v>
       </c>
       <c r="AJ97" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK97" t="s">
         <v>95</v>
@@ -11988,7 +12009,7 @@
         <v>6511</v>
       </c>
       <c r="AN97" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO97">
         <v>65</v>
@@ -12080,7 +12101,7 @@
         <v>91</v>
       </c>
       <c r="AJ98" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK98" t="s">
         <v>95</v>
@@ -12092,7 +12113,7 @@
         <v>6511.01</v>
       </c>
       <c r="AN98" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO98">
         <v>65</v>
@@ -12184,7 +12205,7 @@
         <v>91</v>
       </c>
       <c r="AJ99" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK99" t="s">
         <v>95</v>
@@ -12288,7 +12309,7 @@
         <v>91</v>
       </c>
       <c r="AJ100" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK100" t="s">
         <v>95</v>
@@ -12300,7 +12321,7 @@
         <v>6512</v>
       </c>
       <c r="AN100" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO100">
         <v>65</v>
@@ -12392,7 +12413,7 @@
         <v>91</v>
       </c>
       <c r="AJ101" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK101" t="s">
         <v>95</v>
@@ -12404,7 +12425,7 @@
         <v>6512.01</v>
       </c>
       <c r="AN101" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO101">
         <v>65</v>
@@ -12496,7 +12517,7 @@
         <v>91</v>
       </c>
       <c r="AJ102" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK102" t="s">
         <v>95</v>
@@ -12508,7 +12529,7 @@
         <v>6513</v>
       </c>
       <c r="AN102" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO102">
         <v>65</v>
@@ -12600,7 +12621,7 @@
         <v>91</v>
       </c>
       <c r="AJ103" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK103" t="s">
         <v>95</v>
@@ -12612,7 +12633,7 @@
         <v>6513.01</v>
       </c>
       <c r="AN103" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO103">
         <v>65</v>
@@ -12719,7 +12740,7 @@
         <v>108</v>
       </c>
       <c r="AJ104" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK104" t="s">
         <v>116</v>
@@ -12731,7 +12752,7 @@
         <v>6514</v>
       </c>
       <c r="AN104" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO104">
         <v>65</v>
@@ -12838,7 +12859,7 @@
         <v>108</v>
       </c>
       <c r="AJ105" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK105" t="s">
         <v>116</v>
@@ -12850,7 +12871,7 @@
         <v>6514.01</v>
       </c>
       <c r="AN105" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO105">
         <v>65</v>
@@ -12957,7 +12978,7 @@
         <v>108</v>
       </c>
       <c r="AJ106" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK106" t="s">
         <v>116</v>
@@ -12969,7 +12990,7 @@
         <v>6515</v>
       </c>
       <c r="AN106" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO106">
         <v>65</v>
@@ -13076,7 +13097,7 @@
         <v>108</v>
       </c>
       <c r="AJ107" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK107" t="s">
         <v>116</v>
@@ -13088,7 +13109,7 @@
         <v>6515.01</v>
       </c>
       <c r="AN107" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO107">
         <v>65</v>
@@ -13195,7 +13216,7 @@
         <v>108</v>
       </c>
       <c r="AJ108" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK108" t="s">
         <v>116</v>
@@ -13207,7 +13228,7 @@
         <v>6516</v>
       </c>
       <c r="AN108" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO108">
         <v>65</v>
@@ -13314,7 +13335,7 @@
         <v>108</v>
       </c>
       <c r="AJ109" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK109" t="s">
         <v>116</v>
@@ -13326,7 +13347,7 @@
         <v>6516.01</v>
       </c>
       <c r="AN109" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO109">
         <v>65</v>
@@ -13433,7 +13454,7 @@
         <v>108</v>
       </c>
       <c r="AJ110" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK110" t="s">
         <v>116</v>
@@ -13552,7 +13573,7 @@
         <v>108</v>
       </c>
       <c r="AJ111" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK111" t="s">
         <v>116</v>
@@ -13668,7 +13689,7 @@
         <v>108</v>
       </c>
       <c r="AJ112" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK112" t="s">
         <v>116</v>
@@ -13680,7 +13701,7 @@
         <v>6517</v>
       </c>
       <c r="AN112" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO112">
         <v>65</v>
@@ -13784,7 +13805,7 @@
         <v>108</v>
       </c>
       <c r="AJ113" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK113" t="s">
         <v>116</v>
@@ -13796,7 +13817,7 @@
         <v>6517.01</v>
       </c>
       <c r="AN113" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO113">
         <v>65</v>
@@ -13900,7 +13921,7 @@
         <v>108</v>
       </c>
       <c r="AJ114" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK114" t="s">
         <v>116</v>
@@ -13912,7 +13933,7 @@
         <v>6518</v>
       </c>
       <c r="AN114" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO114">
         <v>65</v>
@@ -14016,7 +14037,7 @@
         <v>108</v>
       </c>
       <c r="AJ115" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK115" t="s">
         <v>116</v>
@@ -14028,7 +14049,7 @@
         <v>6518.01</v>
       </c>
       <c r="AN115" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO115">
         <v>65</v>
@@ -14132,7 +14153,7 @@
         <v>108</v>
       </c>
       <c r="AJ116" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK116" t="s">
         <v>116</v>
@@ -14144,7 +14165,7 @@
         <v>6519</v>
       </c>
       <c r="AN116" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO116">
         <v>65</v>
@@ -14248,7 +14269,7 @@
         <v>108</v>
       </c>
       <c r="AJ117" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK117" t="s">
         <v>116</v>
@@ -14260,7 +14281,7 @@
         <v>6519.01</v>
       </c>
       <c r="AN117" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO117">
         <v>65</v>
@@ -14367,7 +14388,7 @@
         <v>109</v>
       </c>
       <c r="AJ118" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK118" t="s">
         <v>117</v>
@@ -14379,7 +14400,7 @@
         <v>6520</v>
       </c>
       <c r="AN118" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO118">
         <v>65</v>
@@ -14486,7 +14507,7 @@
         <v>109</v>
       </c>
       <c r="AJ119" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK119" t="s">
         <v>117</v>
@@ -14498,7 +14519,7 @@
         <v>6520.01</v>
       </c>
       <c r="AN119" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO119">
         <v>65</v>
@@ -14608,7 +14629,7 @@
         <v>110</v>
       </c>
       <c r="AJ120" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AK120" t="s">
         <v>118</v>
@@ -14620,7 +14641,7 @@
         <v>6521</v>
       </c>
       <c r="AN120" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO120">
         <v>65</v>
@@ -14730,7 +14751,7 @@
         <v>110</v>
       </c>
       <c r="AJ121" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AK121" t="s">
         <v>118</v>
@@ -14742,7 +14763,7 @@
         <v>6521.01</v>
       </c>
       <c r="AN121" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO121">
         <v>65</v>
@@ -14837,7 +14858,7 @@
         <v>3</v>
       </c>
       <c r="AJ122" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK122" t="s">
         <v>95</v>
@@ -14849,7 +14870,7 @@
         <v>6522</v>
       </c>
       <c r="AN122" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO122">
         <v>65</v>
@@ -14944,7 +14965,7 @@
         <v>3</v>
       </c>
       <c r="AJ123" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK123" t="s">
         <v>95</v>
@@ -14956,7 +14977,7 @@
         <v>6522.01</v>
       </c>
       <c r="AN123" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO123">
         <v>65</v>
@@ -15063,7 +15084,7 @@
         <v>108</v>
       </c>
       <c r="AJ124" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK124" t="s">
         <v>116</v>
@@ -15075,7 +15096,7 @@
         <v>6524</v>
       </c>
       <c r="AN124" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO124">
         <v>65</v>
@@ -15182,7 +15203,7 @@
         <v>108</v>
       </c>
       <c r="AJ125" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AK125" t="s">
         <v>116</v>
@@ -15194,7 +15215,7 @@
         <v>6524.01</v>
       </c>
       <c r="AN125" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO125">
         <v>65</v>
@@ -15292,7 +15313,7 @@
         <v>73</v>
       </c>
       <c r="AJ126" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK126" t="s">
         <v>95</v>
@@ -15304,7 +15325,7 @@
         <v>6620</v>
       </c>
       <c r="AN126" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO126">
         <v>66</v>
@@ -15402,7 +15423,7 @@
         <v>73</v>
       </c>
       <c r="AJ127" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK127" t="s">
         <v>95</v>
@@ -15414,7 +15435,7 @@
         <v>6620.01</v>
       </c>
       <c r="AN127" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO127">
         <v>66</v>
@@ -15509,7 +15530,7 @@
         <v>73</v>
       </c>
       <c r="AJ128" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK128" t="s">
         <v>95</v>
@@ -15521,7 +15542,7 @@
         <v>6621</v>
       </c>
       <c r="AN128" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO128">
         <v>66</v>
@@ -15616,7 +15637,7 @@
         <v>73</v>
       </c>
       <c r="AJ129" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK129" t="s">
         <v>95</v>
@@ -15628,7 +15649,7 @@
         <v>6621.01</v>
       </c>
       <c r="AN129" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO129">
         <v>66</v>
@@ -15723,7 +15744,7 @@
         <v>111</v>
       </c>
       <c r="AJ130" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK130" t="s">
         <v>95</v>
@@ -15735,7 +15756,7 @@
         <v>6720</v>
       </c>
       <c r="AN130" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO130">
         <v>67</v>
@@ -15830,7 +15851,7 @@
         <v>111</v>
       </c>
       <c r="AJ131" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK131" t="s">
         <v>95</v>
@@ -15842,7 +15863,7 @@
         <v>6720.01</v>
       </c>
       <c r="AN131" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO131">
         <v>67</v>
@@ -15937,7 +15958,7 @@
         <v>112</v>
       </c>
       <c r="AJ132" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK132" t="s">
         <v>95</v>
@@ -15949,7 +15970,7 @@
         <v>6721</v>
       </c>
       <c r="AN132" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO132">
         <v>67</v>
@@ -16044,7 +16065,7 @@
         <v>112</v>
       </c>
       <c r="AJ133" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK133" t="s">
         <v>95</v>
@@ -16056,7 +16077,7 @@
         <v>6721.01</v>
       </c>
       <c r="AN133" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO133">
         <v>67</v>
@@ -16154,7 +16175,7 @@
         <v>113</v>
       </c>
       <c r="AJ134" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK134" t="s">
         <v>119</v>
@@ -16166,7 +16187,7 @@
         <v>6722</v>
       </c>
       <c r="AN134" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO134">
         <v>67</v>
@@ -16264,7 +16285,7 @@
         <v>113</v>
       </c>
       <c r="AJ135" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK135" t="s">
         <v>119</v>
@@ -16276,7 +16297,7 @@
         <v>6722.01</v>
       </c>
       <c r="AN135" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO135">
         <v>67</v>
@@ -16371,7 +16392,7 @@
         <v>113</v>
       </c>
       <c r="AJ136" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK136" t="s">
         <v>119</v>
@@ -16383,7 +16404,7 @@
         <v>6723</v>
       </c>
       <c r="AN136" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO136">
         <v>67</v>
@@ -16478,7 +16499,7 @@
         <v>113</v>
       </c>
       <c r="AJ137" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AK137" t="s">
         <v>119</v>
@@ -16490,7 +16511,7 @@
         <v>6723.01</v>
       </c>
       <c r="AN137" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO137">
         <v>67</v>
@@ -16594,7 +16615,7 @@
         <v>114</v>
       </c>
       <c r="AJ138" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK138" t="s">
         <v>116</v>
@@ -16606,7 +16627,7 @@
         <v>6724</v>
       </c>
       <c r="AN138" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO138">
         <v>67</v>
@@ -16710,7 +16731,7 @@
         <v>114</v>
       </c>
       <c r="AJ139" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK139" t="s">
         <v>116</v>
@@ -16722,7 +16743,7 @@
         <v>6724.01</v>
       </c>
       <c r="AN139" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO139">
         <v>67</v>
@@ -16862,7 +16883,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4632EB64-3C9B-49A1-A2BE-C39B89F1FE5D}">
-  <dimension ref="A1:AQ171"/>
+  <dimension ref="A1:AQ172"/>
   <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
@@ -17011,16 +17032,16 @@
         <v>121</v>
       </c>
       <c r="AN1" s="30" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AO1" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AP1" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="AQ1" s="2" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:43">
@@ -17118,7 +17139,7 @@
         <v>3000</v>
       </c>
       <c r="AN2" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO2">
         <v>30</v>
@@ -17225,7 +17246,7 @@
         <v>3000.01</v>
       </c>
       <c r="AN3" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO3">
         <v>30</v>
@@ -17332,7 +17353,7 @@
         <v>3000.02</v>
       </c>
       <c r="AN4" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO4">
         <v>30</v>
@@ -17346,7 +17367,7 @@
     </row>
     <row r="5" spans="1:43">
       <c r="A5" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B5">
         <v>9.5</v>
@@ -17358,7 +17379,7 @@
         <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G5" s="5">
         <v>2000</v>
@@ -17425,7 +17446,7 @@
         <v>215</v>
       </c>
       <c r="AG5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AH5" s="1">
         <v>9.5</v>
@@ -17435,7 +17456,7 @@
         <v>3 doors</v>
       </c>
       <c r="AK5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL5" t="s">
         <v>101</v>
@@ -17445,7 +17466,7 @@
         <v>4000</v>
       </c>
       <c r="AN5" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO5">
         <v>40</v>
@@ -17459,7 +17480,7 @@
     </row>
     <row r="6" spans="1:43">
       <c r="A6" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B6">
         <v>11</v>
@@ -17471,7 +17492,7 @@
         <v>87</v>
       </c>
       <c r="F6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G6" s="5">
         <v>2002</v>
@@ -17538,7 +17559,7 @@
         <v>215</v>
       </c>
       <c r="AG6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AH6" s="1">
         <v>11</v>
@@ -17548,7 +17569,7 @@
         <v>3 doors</v>
       </c>
       <c r="AK6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL6" t="s">
         <v>101</v>
@@ -17558,7 +17579,7 @@
         <v>4001</v>
       </c>
       <c r="AN6" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO6">
         <v>40</v>
@@ -17572,7 +17593,7 @@
     </row>
     <row r="7" spans="1:43">
       <c r="A7" s="28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B7">
         <v>9.5</v>
@@ -17644,7 +17665,7 @@
         <v>4002</v>
       </c>
       <c r="AN7" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO7">
         <v>40</v>
@@ -17658,7 +17679,7 @@
     </row>
     <row r="8" spans="1:43">
       <c r="A8" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B8">
         <v>12</v>
@@ -17733,7 +17754,7 @@
         <v>4003</v>
       </c>
       <c r="AN8" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO8">
         <v>40</v>
@@ -17747,7 +17768,7 @@
     </row>
     <row r="9" spans="1:43">
       <c r="A9" s="28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B9">
         <v>12</v>
@@ -17797,7 +17818,7 @@
     </row>
     <row r="10" spans="1:43">
       <c r="A10" s="28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B10">
         <v>18</v>
@@ -17878,7 +17899,7 @@
         <v>4004</v>
       </c>
       <c r="AN10" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO10">
         <v>40</v>
@@ -17892,7 +17913,7 @@
     </row>
     <row r="11" spans="1:43">
       <c r="A11" s="28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B11">
         <v>18</v>
@@ -17942,7 +17963,7 @@
     </row>
     <row r="12" spans="1:43">
       <c r="A12" s="28" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B12">
         <v>12</v>
@@ -18017,7 +18038,7 @@
         <v>4005</v>
       </c>
       <c r="AN12" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO12">
         <v>40</v>
@@ -18031,7 +18052,7 @@
     </row>
     <row r="13" spans="1:43">
       <c r="A13" s="28" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B13">
         <v>19</v>
@@ -18118,7 +18139,7 @@
         <v>4006</v>
       </c>
       <c r="AN13" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO13">
         <v>40</v>
@@ -18228,7 +18249,7 @@
         <v>4007</v>
       </c>
       <c r="AN14" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO14">
         <v>40</v>
@@ -18341,7 +18362,7 @@
         <v>4008</v>
       </c>
       <c r="AN15" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO15">
         <v>40</v>
@@ -18451,7 +18472,7 @@
         <v>4009</v>
       </c>
       <c r="AN16" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO16">
         <v>40</v>
@@ -18564,7 +18585,7 @@
         <v>4010</v>
       </c>
       <c r="AN17" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO17">
         <v>40</v>
@@ -18674,7 +18695,7 @@
         <v>4011</v>
       </c>
       <c r="AN18" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO18">
         <v>40</v>
@@ -18688,7 +18709,7 @@
     </row>
     <row r="19" spans="1:43">
       <c r="A19" s="28" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B19">
         <v>12</v>
@@ -18757,7 +18778,7 @@
         <v>4012</v>
       </c>
       <c r="AN19" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO19">
         <v>40</v>
@@ -18771,7 +18792,7 @@
     </row>
     <row r="20" spans="1:43">
       <c r="A20" s="28" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -18852,7 +18873,7 @@
         <v>4013</v>
       </c>
       <c r="AN20" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO20">
         <v>40</v>
@@ -18866,7 +18887,7 @@
     </row>
     <row r="21" spans="1:43">
       <c r="A21" s="28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B21">
         <v>9.5</v>
@@ -18878,7 +18899,7 @@
         <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G21" s="5">
         <v>2000</v>
@@ -18942,7 +18963,7 @@
         <v>215</v>
       </c>
       <c r="AG21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AH21" s="1">
         <v>9.5</v>
@@ -18952,7 +18973,7 @@
         <v>2 doors</v>
       </c>
       <c r="AK21" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s">
         <v>120</v>
@@ -18962,7 +18983,7 @@
         <v>4014</v>
       </c>
       <c r="AN21" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO21">
         <v>40</v>
@@ -18976,7 +18997,7 @@
     </row>
     <row r="22" spans="1:43">
       <c r="A22" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B22">
         <v>11</v>
@@ -18988,7 +19009,7 @@
         <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G22" s="5">
         <v>2003</v>
@@ -19052,7 +19073,7 @@
         <v>215</v>
       </c>
       <c r="AG22" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AH22" s="1">
         <v>11</v>
@@ -19062,7 +19083,7 @@
         <v>2 doors</v>
       </c>
       <c r="AK22" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL22" t="s">
         <v>120</v>
@@ -19072,7 +19093,7 @@
         <v>4015</v>
       </c>
       <c r="AN22" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO22">
         <v>40</v>
@@ -19086,7 +19107,7 @@
     </row>
     <row r="23" spans="1:43">
       <c r="A23" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B23">
         <v>12</v>
@@ -19098,7 +19119,7 @@
         <v>87</v>
       </c>
       <c r="F23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G23" s="5">
         <v>2004</v>
@@ -19162,7 +19183,7 @@
         <v>215</v>
       </c>
       <c r="AG23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AH23" s="1">
         <v>12</v>
@@ -19182,7 +19203,7 @@
         <v>4016</v>
       </c>
       <c r="AN23" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO23">
         <v>40</v>
@@ -19292,7 +19313,7 @@
         <v>4017</v>
       </c>
       <c r="AN24" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO24">
         <v>40</v>
@@ -19306,7 +19327,7 @@
     </row>
     <row r="25" spans="1:43">
       <c r="A25" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B25">
         <v>9.5</v>
@@ -19318,7 +19339,7 @@
         <v>87</v>
       </c>
       <c r="F25" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G25" s="5">
         <v>2000</v>
@@ -19382,7 +19403,7 @@
         <v>215</v>
       </c>
       <c r="AG25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AH25" s="1">
         <v>9.5</v>
@@ -19392,17 +19413,17 @@
         <v>2 doors</v>
       </c>
       <c r="AK25" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AL25" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM25" s="9">
         <f t="shared" si="5"/>
         <v>4018</v>
       </c>
       <c r="AN25" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO25">
         <v>40</v>
@@ -19416,7 +19437,7 @@
     </row>
     <row r="26" spans="1:43">
       <c r="A26" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B26">
         <v>11</v>
@@ -19428,7 +19449,7 @@
         <v>87</v>
       </c>
       <c r="F26" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G26" s="5">
         <v>2001</v>
@@ -19492,7 +19513,7 @@
         <v>215</v>
       </c>
       <c r="AG26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AH26" s="1">
         <v>11</v>
@@ -19502,17 +19523,17 @@
         <v>2 doors</v>
       </c>
       <c r="AK26" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL26" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM26" s="9">
         <f t="shared" si="5"/>
         <v>4019</v>
       </c>
       <c r="AN26" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO26">
         <v>40</v>
@@ -19526,7 +19547,7 @@
     </row>
     <row r="27" spans="1:43">
       <c r="A27" s="28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B27">
         <v>12</v>
@@ -19538,7 +19559,7 @@
         <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G27" s="5">
         <v>2005</v>
@@ -19602,7 +19623,7 @@
         <v>215</v>
       </c>
       <c r="AG27" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AH27" s="1">
         <v>12</v>
@@ -19615,14 +19636,14 @@
         <v>95</v>
       </c>
       <c r="AL27" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM27" s="9">
         <f t="shared" si="5"/>
         <v>4020</v>
       </c>
       <c r="AN27" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO27">
         <v>40</v>
@@ -19725,14 +19746,14 @@
         <v>95</v>
       </c>
       <c r="AL28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM28" s="9">
         <f t="shared" si="5"/>
         <v>4021</v>
       </c>
       <c r="AN28" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO28">
         <v>40</v>
@@ -19746,10 +19767,10 @@
     </row>
     <row r="29" spans="1:43">
       <c r="A29" s="28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -19758,7 +19779,7 @@
         <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G29" s="5">
         <v>2005</v>
@@ -19822,7 +19843,7 @@
         <v>215</v>
       </c>
       <c r="AG29" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AH29" s="1">
         <v>9.5</v>
@@ -19832,17 +19853,17 @@
         <v>2 doors</v>
       </c>
       <c r="AK29" t="s">
+        <v>243</v>
+      </c>
+      <c r="AL29" t="s">
         <v>245</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>247</v>
       </c>
       <c r="AM29" s="9">
         <f t="shared" si="5"/>
         <v>4022</v>
       </c>
       <c r="AN29" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO29">
         <v>40</v>
@@ -19856,10 +19877,10 @@
     </row>
     <row r="30" spans="1:43">
       <c r="A30" s="28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B30" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -19868,7 +19889,7 @@
         <v>87</v>
       </c>
       <c r="F30" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G30" s="5">
         <v>2003</v>
@@ -19932,7 +19953,7 @@
         <v>215</v>
       </c>
       <c r="AG30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AH30" s="1">
         <v>11</v>
@@ -19942,17 +19963,17 @@
         <v>2 doors</v>
       </c>
       <c r="AK30" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL30" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM30" s="9">
         <f t="shared" si="5"/>
         <v>4023</v>
       </c>
       <c r="AN30" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO30">
         <v>40</v>
@@ -19966,7 +19987,7 @@
     </row>
     <row r="31" spans="1:43">
       <c r="A31" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B31">
         <v>12</v>
@@ -19978,7 +19999,7 @@
         <v>87</v>
       </c>
       <c r="F31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G31" s="5">
         <v>2008</v>
@@ -20042,7 +20063,7 @@
         <v>215</v>
       </c>
       <c r="AG31" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AH31" s="1">
         <v>12</v>
@@ -20055,14 +20076,14 @@
         <v>95</v>
       </c>
       <c r="AL31" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM31" s="9">
         <f t="shared" si="5"/>
         <v>4024</v>
       </c>
       <c r="AN31" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO31">
         <v>40</v>
@@ -20165,14 +20186,14 @@
         <v>96</v>
       </c>
       <c r="AL32" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM32" s="9">
         <f t="shared" si="5"/>
         <v>4025</v>
       </c>
       <c r="AN32" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO32">
         <v>40</v>
@@ -20275,14 +20296,14 @@
         <v>95</v>
       </c>
       <c r="AL33" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM33" s="9">
         <f t="shared" si="5"/>
         <v>4026</v>
       </c>
       <c r="AN33" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO33">
         <v>40</v>
@@ -20398,7 +20419,7 @@
         <v>5500</v>
       </c>
       <c r="AN34" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO34">
         <v>55</v>
@@ -20514,7 +20535,7 @@
         <v>5500.01</v>
       </c>
       <c r="AN35" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO35">
         <v>55</v>
@@ -20746,7 +20767,7 @@
         <v>5500.03</v>
       </c>
       <c r="AN37" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AO37">
         <v>55</v>
@@ -20859,7 +20880,7 @@
         <v>5501</v>
       </c>
       <c r="AN38" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO38">
         <v>55</v>
@@ -20972,7 +20993,7 @@
         <v>5501.01</v>
       </c>
       <c r="AN39" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO39">
         <v>55</v>
@@ -21201,7 +21222,7 @@
         <v>5502</v>
       </c>
       <c r="AN41" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO41">
         <v>55</v>
@@ -21317,7 +21338,7 @@
         <v>5502.01</v>
       </c>
       <c r="AN42" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO42">
         <v>55</v>
@@ -21433,7 +21454,7 @@
         <v>5503</v>
       </c>
       <c r="AN43" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO43">
         <v>55</v>
@@ -21549,7 +21570,7 @@
         <v>5503.01</v>
       </c>
       <c r="AN44" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO44">
         <v>55</v>
@@ -21665,7 +21686,7 @@
         <v>5504</v>
       </c>
       <c r="AN45" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO45">
         <v>55</v>
@@ -21781,7 +21802,7 @@
         <v>5504.01</v>
       </c>
       <c r="AN46" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO46">
         <v>55</v>
@@ -21894,7 +21915,7 @@
         <v>5505</v>
       </c>
       <c r="AN47" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO47">
         <v>55</v>
@@ -22007,7 +22028,7 @@
         <v>5505.01</v>
       </c>
       <c r="AN48" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO48">
         <v>55</v>
@@ -22120,7 +22141,7 @@
         <v>5506</v>
       </c>
       <c r="AN49" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO49">
         <v>55</v>
@@ -22233,7 +22254,7 @@
         <v>5506.01</v>
       </c>
       <c r="AN50" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO50">
         <v>55</v>
@@ -22346,7 +22367,7 @@
         <v>5507</v>
       </c>
       <c r="AN51" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO51">
         <v>55</v>
@@ -22459,7 +22480,7 @@
         <v>5507.01</v>
       </c>
       <c r="AN52" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO52">
         <v>55</v>
@@ -22584,7 +22605,7 @@
         <v>5508</v>
       </c>
       <c r="AN53" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO53">
         <v>55</v>
@@ -22709,7 +22730,7 @@
         <v>5508.01</v>
       </c>
       <c r="AN54" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO54">
         <v>55</v>
@@ -22834,7 +22855,7 @@
         <v>5509</v>
       </c>
       <c r="AN55" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO55">
         <v>55</v>
@@ -22959,7 +22980,7 @@
         <v>5509.01</v>
       </c>
       <c r="AN56" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO56">
         <v>55</v>
@@ -23084,7 +23105,7 @@
         <v>5510</v>
       </c>
       <c r="AN57" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO57">
         <v>55</v>
@@ -23209,7 +23230,7 @@
         <v>5510.01</v>
       </c>
       <c r="AN58" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO58">
         <v>55</v>
@@ -23331,7 +23352,7 @@
         <v>5511</v>
       </c>
       <c r="AN59" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO59">
         <v>55</v>
@@ -23453,7 +23474,7 @@
         <v>5511.01</v>
       </c>
       <c r="AN60" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO60">
         <v>55</v>
@@ -23575,7 +23596,7 @@
         <v>5512</v>
       </c>
       <c r="AN61" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO61">
         <v>55</v>
@@ -23697,7 +23718,7 @@
         <v>5512.01</v>
       </c>
       <c r="AN62" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO62">
         <v>55</v>
@@ -23819,7 +23840,7 @@
         <v>5513</v>
       </c>
       <c r="AN63" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO63">
         <v>55</v>
@@ -23941,7 +23962,7 @@
         <v>5513.01</v>
       </c>
       <c r="AN64" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO64">
         <v>55</v>
@@ -24054,7 +24075,7 @@
         <v>5620</v>
       </c>
       <c r="AN65" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO65">
         <v>56</v>
@@ -24167,7 +24188,7 @@
         <v>5621</v>
       </c>
       <c r="AN66" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO66">
         <v>56</v>
@@ -24283,7 +24304,7 @@
         <v>5622</v>
       </c>
       <c r="AN67" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO67">
         <v>56</v>
@@ -24396,7 +24417,7 @@
         <v>5720</v>
       </c>
       <c r="AN68" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO68">
         <v>57</v>
@@ -24509,7 +24530,7 @@
         <v>5721</v>
       </c>
       <c r="AN69" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO69">
         <v>57</v>
@@ -24622,7 +24643,7 @@
         <v>5721.01</v>
       </c>
       <c r="AN70" s="29" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO70">
         <v>57</v>
@@ -24700,7 +24721,7 @@
         <v>160</v>
       </c>
       <c r="Y71" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Z71" s="5">
         <v>8</v>
@@ -24735,7 +24756,7 @@
         <v>5721.02</v>
       </c>
       <c r="AN71" s="29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AO71">
         <v>57</v>
@@ -24851,7 +24872,7 @@
         <v>5722</v>
       </c>
       <c r="AN72" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO72">
         <v>57</v>
@@ -24964,7 +24985,7 @@
         <v>6500</v>
       </c>
       <c r="AN73" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO73">
         <v>65</v>
@@ -25077,7 +25098,7 @@
         <v>6500.01</v>
       </c>
       <c r="AN74" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO74">
         <v>65</v>
@@ -25202,7 +25223,7 @@
         <v>6502</v>
       </c>
       <c r="AN75" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO75">
         <v>65</v>
@@ -25327,7 +25348,7 @@
         <v>6502.01</v>
       </c>
       <c r="AN76" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO76">
         <v>65</v>
@@ -25443,7 +25464,7 @@
         <v>6504</v>
       </c>
       <c r="AN77" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO77">
         <v>65</v>
@@ -25559,7 +25580,7 @@
         <v>6504.01</v>
       </c>
       <c r="AN78" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO78">
         <v>65</v>
@@ -25791,7 +25812,7 @@
         <v>6505</v>
       </c>
       <c r="AN80" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO80">
         <v>65</v>
@@ -25907,7 +25928,7 @@
         <v>6505.01</v>
       </c>
       <c r="AN81" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO81">
         <v>65</v>
@@ -26020,7 +26041,7 @@
         <v>6506</v>
       </c>
       <c r="AN82" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO82">
         <v>65</v>
@@ -26133,7 +26154,7 @@
         <v>6506.01</v>
       </c>
       <c r="AN83" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO83">
         <v>65</v>
@@ -26246,7 +26267,7 @@
         <v>6507</v>
       </c>
       <c r="AN84" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO84">
         <v>65</v>
@@ -26359,7 +26380,7 @@
         <v>6507.01</v>
       </c>
       <c r="AN85" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO85">
         <v>65</v>
@@ -26472,7 +26493,7 @@
         <v>6508</v>
       </c>
       <c r="AN86" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO86">
         <v>65</v>
@@ -26585,7 +26606,7 @@
         <v>6508.01</v>
       </c>
       <c r="AN87" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO87">
         <v>65</v>
@@ -27150,7 +27171,7 @@
         <v>6509</v>
       </c>
       <c r="AN92" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO92">
         <v>65</v>
@@ -27263,7 +27284,7 @@
         <v>6509.01</v>
       </c>
       <c r="AN93" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO93">
         <v>65</v>
@@ -27376,7 +27397,7 @@
         <v>6510</v>
       </c>
       <c r="AN94" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO94">
         <v>65</v>
@@ -27489,7 +27510,7 @@
         <v>6510.01</v>
       </c>
       <c r="AN95" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO95">
         <v>65</v>
@@ -28729,7 +28750,7 @@
         <v>6511</v>
       </c>
       <c r="AN106" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO106">
         <v>65</v>
@@ -28839,7 +28860,7 @@
         <v>6511.01</v>
       </c>
       <c r="AN107" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO107">
         <v>65</v>
@@ -29059,7 +29080,7 @@
         <v>6512</v>
       </c>
       <c r="AN109" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO109">
         <v>65</v>
@@ -29169,7 +29190,7 @@
         <v>6512.01</v>
       </c>
       <c r="AN110" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO110">
         <v>65</v>
@@ -29279,7 +29300,7 @@
         <v>6513</v>
       </c>
       <c r="AN111" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO111">
         <v>65</v>
@@ -29389,7 +29410,7 @@
         <v>6513.01</v>
       </c>
       <c r="AN112" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO112">
         <v>65</v>
@@ -29514,7 +29535,7 @@
         <v>6514</v>
       </c>
       <c r="AN113" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO113">
         <v>65</v>
@@ -29639,7 +29660,7 @@
         <v>6514.01</v>
       </c>
       <c r="AN114" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO114">
         <v>65</v>
@@ -29764,7 +29785,7 @@
         <v>6515</v>
       </c>
       <c r="AN115" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO115">
         <v>65</v>
@@ -29889,7 +29910,7 @@
         <v>6515.01</v>
       </c>
       <c r="AN116" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO116">
         <v>65</v>
@@ -30014,7 +30035,7 @@
         <v>6516</v>
       </c>
       <c r="AN117" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO117">
         <v>65</v>
@@ -30139,7 +30160,7 @@
         <v>6516.01</v>
       </c>
       <c r="AN118" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO118">
         <v>65</v>
@@ -30511,7 +30532,7 @@
         <v>6517</v>
       </c>
       <c r="AN121" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO121">
         <v>65</v>
@@ -30633,7 +30654,7 @@
         <v>6517.01</v>
       </c>
       <c r="AN122" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO122">
         <v>65</v>
@@ -30755,7 +30776,7 @@
         <v>6518</v>
       </c>
       <c r="AN123" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO123">
         <v>65</v>
@@ -30877,7 +30898,7 @@
         <v>6518.01</v>
       </c>
       <c r="AN124" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO124">
         <v>65</v>
@@ -30999,7 +31020,7 @@
         <v>6519</v>
       </c>
       <c r="AN125" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO125">
         <v>65</v>
@@ -31121,7 +31142,7 @@
         <v>6519.01</v>
       </c>
       <c r="AN126" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO126">
         <v>65</v>
@@ -31246,7 +31267,7 @@
         <v>6520</v>
       </c>
       <c r="AN127" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO127">
         <v>65</v>
@@ -31371,7 +31392,7 @@
         <v>6520.01</v>
       </c>
       <c r="AN128" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO128">
         <v>65</v>
@@ -31499,7 +31520,7 @@
         <v>6521</v>
       </c>
       <c r="AN129" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO129">
         <v>65</v>
@@ -31627,7 +31648,7 @@
         <v>6521.01</v>
       </c>
       <c r="AN130" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO130">
         <v>65</v>
@@ -31740,7 +31761,7 @@
         <v>6522</v>
       </c>
       <c r="AN131" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO131">
         <v>65</v>
@@ -31790,11 +31811,11 @@
         <v>14</v>
       </c>
       <c r="P132" s="6">
-        <f t="shared" ref="P132:P163" si="27">SUM(K132:O132)</f>
+        <f t="shared" ref="P132:P148" si="27">SUM(K132:O132)</f>
         <v>42</v>
       </c>
       <c r="Q132" s="6">
-        <f t="shared" ref="Q132:Q163" si="28">IF(E132="diesel", ((V132+(T132/10))/2)+(P132/14), IF(OR(E132="cng", E132="hybrid"), ((V132+(T132/10))/2*1.2)+(P132/14), IF(E132="electric", ((V132+(T132/10))/2*1.5)+(P132/14), 0)))</f>
+        <f t="shared" ref="Q132:Q148" si="28">IF(E132="diesel", ((V132+(T132/10))/2)+(P132/14), IF(OR(E132="cng", E132="hybrid"), ((V132+(T132/10))/2*1.2)+(P132/14), IF(E132="electric", ((V132+(T132/10))/2*1.5)+(P132/14), 0)))</f>
         <v>23.250999999999998</v>
       </c>
       <c r="R132" s="6">
@@ -31805,7 +31826,7 @@
         <v>75</v>
       </c>
       <c r="T132" s="7">
-        <f t="shared" ref="T132:T163" si="30">U132*1.341</f>
+        <f t="shared" ref="T132:T162" si="30">U132*1.341</f>
         <v>295.02</v>
       </c>
       <c r="U132" s="5">
@@ -31839,7 +31860,7 @@
         <v>3</v>
       </c>
       <c r="AJ132" s="4" t="str">
-        <f t="shared" ref="AJ132:AJ148" si="31">C132 &amp; " doors"</f>
+        <f t="shared" ref="AJ132:AJ162" si="31">C132 &amp; " doors"</f>
         <v>3 doors</v>
       </c>
       <c r="AK132" t="s">
@@ -31853,7 +31874,7 @@
         <v>6522.01</v>
       </c>
       <c r="AN132" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO132">
         <v>65</v>
@@ -31978,7 +31999,7 @@
         <v>6524</v>
       </c>
       <c r="AN133" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO133">
         <v>65</v>
@@ -32103,7 +32124,7 @@
         <v>6524.01</v>
       </c>
       <c r="AN134" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO134">
         <v>65</v>
@@ -32219,7 +32240,7 @@
         <v>6620</v>
       </c>
       <c r="AN135" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO135">
         <v>66</v>
@@ -32335,7 +32356,7 @@
         <v>6620.01</v>
       </c>
       <c r="AN136" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO136">
         <v>66</v>
@@ -32448,7 +32469,7 @@
         <v>6621</v>
       </c>
       <c r="AN137" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO137">
         <v>66</v>
@@ -32561,7 +32582,7 @@
         <v>6621.01</v>
       </c>
       <c r="AN138" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO138">
         <v>66</v>
@@ -32674,7 +32695,7 @@
         <v>6720</v>
       </c>
       <c r="AN139" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO139">
         <v>67</v>
@@ -32787,7 +32808,7 @@
         <v>6720.01</v>
       </c>
       <c r="AN140" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO140">
         <v>67</v>
@@ -32900,7 +32921,7 @@
         <v>6721</v>
       </c>
       <c r="AN141" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO141">
         <v>67</v>
@@ -33013,7 +33034,7 @@
         <v>6721.01</v>
       </c>
       <c r="AN142" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO142">
         <v>67</v>
@@ -33129,7 +33150,7 @@
         <v>6722</v>
       </c>
       <c r="AN143" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO143">
         <v>67</v>
@@ -33245,7 +33266,7 @@
         <v>6722.01</v>
       </c>
       <c r="AN144" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO144">
         <v>67</v>
@@ -33358,7 +33379,7 @@
         <v>6723</v>
       </c>
       <c r="AN145" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO145">
         <v>67</v>
@@ -33471,7 +33492,7 @@
         <v>6723.01</v>
       </c>
       <c r="AN146" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO146">
         <v>67</v>
@@ -33593,7 +33614,7 @@
         <v>6724</v>
       </c>
       <c r="AN147" s="29" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="AO147">
         <v>67</v>
@@ -33715,7 +33736,7 @@
         <v>6724.01</v>
       </c>
       <c r="AN148" s="29" t="s">
-        <v>221</v>
+        <v>109</v>
       </c>
       <c r="AO148">
         <v>67</v>
@@ -33728,122 +33749,983 @@
       </c>
     </row>
     <row r="149" spans="1:43">
-      <c r="P149" s="6"/>
-      <c r="Q149" s="6"/>
-      <c r="R149" s="6"/>
+      <c r="A149" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="B149" t="s">
+        <v>72</v>
+      </c>
+      <c r="C149">
+        <v>3</v>
+      </c>
+      <c r="E149" t="s">
+        <v>87</v>
+      </c>
+      <c r="H149" s="5">
+        <v>20</v>
+      </c>
+      <c r="I149" s="5">
+        <v>25</v>
+      </c>
+      <c r="J149" s="5">
+        <v>20</v>
+      </c>
+      <c r="K149" s="5">
+        <v>14</v>
+      </c>
+      <c r="L149" s="5">
+        <v>14</v>
+      </c>
+      <c r="M149" s="5">
+        <v>14</v>
+      </c>
+      <c r="P149" s="6">
+        <f t="shared" ref="P149:P162" si="33">SUM(K149:O149)</f>
+        <v>42</v>
+      </c>
+      <c r="Q149" s="6">
+        <f t="shared" ref="Q149:Q162" si="34">IF(E149="diesel", ((V149+(T149/10))/2)+(P149/14), IF(OR(E149="cng", E149="hybrid"), ((V149+(T149/10))/2*1.2)+(P149/14), IF(E149="electric", ((V149+(T149/10))/2*1.5)+(P149/14), 0)))</f>
+        <v>3</v>
+      </c>
+      <c r="R149" s="6">
+        <f t="shared" ref="R149:R162" si="35">IF(E149="diesel", ((V149+(W149/15)+T149)/10)+(P149/14), IF(OR(E149="cng", E149="hybrid"), ((V149+(W149/15)+T149)/10*0.8)+(P149/14), IF(E149="electric", ((V149+(W149/15)+T149)/10*0.5)+(P149/14), 0)))</f>
+        <v>3</v>
+      </c>
+      <c r="S149" s="5">
+        <v>80</v>
+      </c>
+      <c r="T149" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X149" s="5">
+        <v>200</v>
+      </c>
+      <c r="Y149" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z149" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA149" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ149" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>3 doors</v>
+      </c>
     </row>
     <row r="150" spans="1:43">
-      <c r="P150" s="6"/>
-      <c r="Q150" s="6"/>
-      <c r="R150" s="6"/>
+      <c r="A150" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="B150" t="s">
+        <v>72</v>
+      </c>
+      <c r="C150">
+        <v>3</v>
+      </c>
+      <c r="E150" t="s">
+        <v>87</v>
+      </c>
+      <c r="H150" s="5">
+        <v>20</v>
+      </c>
+      <c r="I150" s="5">
+        <v>25</v>
+      </c>
+      <c r="J150" s="5">
+        <v>20</v>
+      </c>
+      <c r="K150" s="5">
+        <v>14</v>
+      </c>
+      <c r="L150" s="5">
+        <v>14</v>
+      </c>
+      <c r="M150" s="5">
+        <v>14</v>
+      </c>
+      <c r="P150" s="6">
+        <f t="shared" si="33"/>
+        <v>42</v>
+      </c>
+      <c r="Q150" s="6">
+        <f t="shared" si="34"/>
+        <v>3</v>
+      </c>
+      <c r="R150" s="6">
+        <f t="shared" si="35"/>
+        <v>3</v>
+      </c>
+      <c r="S150" s="5">
+        <v>80</v>
+      </c>
+      <c r="T150" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X150" s="5">
+        <v>200</v>
+      </c>
+      <c r="Y150" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z150" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA150" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ150" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>3 doors</v>
+      </c>
     </row>
     <row r="151" spans="1:43">
-      <c r="P151" s="6"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="6"/>
+      <c r="A151" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="B151" t="s">
+        <v>72</v>
+      </c>
+      <c r="C151">
+        <v>3</v>
+      </c>
+      <c r="E151" t="s">
+        <v>87</v>
+      </c>
+      <c r="H151" s="5">
+        <v>20</v>
+      </c>
+      <c r="I151" s="5">
+        <v>25</v>
+      </c>
+      <c r="J151" s="5">
+        <v>20</v>
+      </c>
+      <c r="P151" s="6">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Q151" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="R151" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="T151" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X151" s="5">
+        <v>200</v>
+      </c>
+      <c r="Y151" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z151" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA151" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ151" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>3 doors</v>
+      </c>
     </row>
     <row r="152" spans="1:43">
-      <c r="P152" s="6"/>
-      <c r="Q152" s="6"/>
-      <c r="R152" s="6"/>
+      <c r="A152" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="B152" t="s">
+        <v>72</v>
+      </c>
+      <c r="C152">
+        <v>3</v>
+      </c>
+      <c r="E152" t="s">
+        <v>87</v>
+      </c>
+      <c r="H152" s="5">
+        <v>20</v>
+      </c>
+      <c r="I152" s="5">
+        <v>25</v>
+      </c>
+      <c r="J152" s="5">
+        <v>20</v>
+      </c>
+      <c r="P152" s="6">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Q152" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="R152" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="T152" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X152" s="5">
+        <v>200</v>
+      </c>
+      <c r="Y152" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z152" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA152" s="5">
+        <v>5</v>
+      </c>
       <c r="AC152" s="5" t="s">
         <v>76</v>
       </c>
+      <c r="AJ152" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>3 doors</v>
+      </c>
     </row>
     <row r="153" spans="1:43">
-      <c r="P153" s="6"/>
-      <c r="Q153" s="6"/>
-      <c r="R153" s="6"/>
+      <c r="A153" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="B153" t="s">
+        <v>72</v>
+      </c>
+      <c r="C153">
+        <v>2</v>
+      </c>
+      <c r="E153" t="s">
+        <v>87</v>
+      </c>
+      <c r="H153" s="5">
+        <v>20</v>
+      </c>
+      <c r="I153" s="5">
+        <v>25</v>
+      </c>
+      <c r="J153" s="5">
+        <v>20</v>
+      </c>
+      <c r="P153" s="6">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Q153" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="R153" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="T153" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X153" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y153" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z153" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA153" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ153" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>2 doors</v>
+      </c>
     </row>
     <row r="154" spans="1:43">
-      <c r="P154" s="6"/>
-      <c r="Q154" s="6"/>
-      <c r="R154" s="6"/>
+      <c r="A154" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="B154" t="s">
+        <v>72</v>
+      </c>
+      <c r="C154">
+        <v>2</v>
+      </c>
+      <c r="E154" t="s">
+        <v>87</v>
+      </c>
+      <c r="H154" s="5">
+        <v>20</v>
+      </c>
+      <c r="I154" s="5">
+        <v>25</v>
+      </c>
+      <c r="J154" s="5">
+        <v>20</v>
+      </c>
+      <c r="P154" s="6">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Q154" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="R154" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="T154" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X154" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y154" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z154" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA154" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ154" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>2 doors</v>
+      </c>
     </row>
     <row r="155" spans="1:43">
-      <c r="P155" s="6"/>
-      <c r="Q155" s="6"/>
-      <c r="R155" s="6"/>
+      <c r="A155" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="B155" t="s">
+        <v>72</v>
+      </c>
+      <c r="C155">
+        <v>3</v>
+      </c>
+      <c r="E155" t="s">
+        <v>87</v>
+      </c>
+      <c r="H155" s="5">
+        <v>20</v>
+      </c>
+      <c r="I155" s="5">
+        <v>25</v>
+      </c>
+      <c r="J155" s="5">
+        <v>20</v>
+      </c>
+      <c r="K155" s="5">
+        <v>14</v>
+      </c>
+      <c r="L155" s="5">
+        <v>14</v>
+      </c>
+      <c r="M155" s="5">
+        <v>14</v>
+      </c>
+      <c r="P155" s="6">
+        <f t="shared" si="33"/>
+        <v>42</v>
+      </c>
+      <c r="Q155" s="6">
+        <f t="shared" si="34"/>
+        <v>9</v>
+      </c>
+      <c r="R155" s="6">
+        <f t="shared" si="35"/>
+        <v>4.7733333333333334</v>
+      </c>
+      <c r="T155" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="V155" s="5">
+        <v>12</v>
+      </c>
+      <c r="W155" s="5">
+        <v>86</v>
+      </c>
+      <c r="X155" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y155" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z155" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA155" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ155" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>3 doors</v>
+      </c>
     </row>
     <row r="156" spans="1:43">
-      <c r="P156" s="6"/>
-      <c r="Q156" s="6"/>
-      <c r="R156" s="6"/>
+      <c r="A156" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="B156" t="s">
+        <v>72</v>
+      </c>
+      <c r="C156">
+        <v>3</v>
+      </c>
+      <c r="E156" t="s">
+        <v>87</v>
+      </c>
+      <c r="H156" s="5">
+        <v>20</v>
+      </c>
+      <c r="I156" s="5">
+        <v>25</v>
+      </c>
+      <c r="J156" s="5">
+        <v>20</v>
+      </c>
+      <c r="K156" s="5">
+        <v>14</v>
+      </c>
+      <c r="L156" s="5">
+        <v>14</v>
+      </c>
+      <c r="M156" s="5">
+        <v>14</v>
+      </c>
+      <c r="P156" s="6">
+        <f t="shared" si="33"/>
+        <v>42</v>
+      </c>
+      <c r="Q156" s="6">
+        <f t="shared" si="34"/>
+        <v>9</v>
+      </c>
+      <c r="R156" s="6">
+        <f t="shared" si="35"/>
+        <v>4.7733333333333334</v>
+      </c>
+      <c r="T156" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="V156" s="5">
+        <v>12</v>
+      </c>
+      <c r="W156" s="5">
+        <v>86</v>
+      </c>
+      <c r="X156" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y156" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z156" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA156" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ156" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>3 doors</v>
+      </c>
     </row>
     <row r="157" spans="1:43">
-      <c r="P157" s="6"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="6"/>
+      <c r="A157" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B157" t="s">
+        <v>265</v>
+      </c>
+      <c r="C157">
+        <v>4</v>
+      </c>
+      <c r="E157" t="s">
+        <v>87</v>
+      </c>
+      <c r="G157" s="5">
+        <v>2003</v>
+      </c>
+      <c r="H157" s="5">
+        <v>20</v>
+      </c>
+      <c r="I157" s="5">
+        <v>25</v>
+      </c>
+      <c r="J157" s="5">
+        <v>20</v>
+      </c>
+      <c r="K157" s="5">
+        <v>14</v>
+      </c>
+      <c r="L157" s="5">
+        <v>14</v>
+      </c>
+      <c r="M157" s="5">
+        <v>14</v>
+      </c>
+      <c r="N157" s="5">
+        <v>14</v>
+      </c>
+      <c r="P157" s="6">
+        <f t="shared" si="33"/>
+        <v>56</v>
+      </c>
+      <c r="Q157" s="6">
+        <f t="shared" si="34"/>
+        <v>4</v>
+      </c>
+      <c r="R157" s="6">
+        <f t="shared" si="35"/>
+        <v>4</v>
+      </c>
+      <c r="T157" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X157" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y157" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z157" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA157" s="5">
+        <v>2</v>
+      </c>
+      <c r="AB157" s="5">
+        <v>8</v>
+      </c>
+      <c r="AC157" s="5">
+        <v>2</v>
+      </c>
+      <c r="AJ157" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>4 doors</v>
+      </c>
     </row>
     <row r="158" spans="1:43">
-      <c r="P158" s="6"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="6"/>
+      <c r="A158" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B158" t="s">
+        <v>265</v>
+      </c>
+      <c r="C158">
+        <v>4</v>
+      </c>
+      <c r="E158" t="s">
+        <v>87</v>
+      </c>
+      <c r="G158" s="5">
+        <v>2003</v>
+      </c>
+      <c r="H158" s="5">
+        <v>20</v>
+      </c>
+      <c r="I158" s="5">
+        <v>25</v>
+      </c>
+      <c r="J158" s="5">
+        <v>20</v>
+      </c>
+      <c r="K158" s="5">
+        <v>14</v>
+      </c>
+      <c r="L158" s="5">
+        <v>14</v>
+      </c>
+      <c r="M158" s="5">
+        <v>14</v>
+      </c>
+      <c r="N158" s="5">
+        <v>14</v>
+      </c>
+      <c r="P158" s="6">
+        <f t="shared" si="33"/>
+        <v>56</v>
+      </c>
+      <c r="Q158" s="6">
+        <f t="shared" si="34"/>
+        <v>4</v>
+      </c>
+      <c r="R158" s="6">
+        <f t="shared" si="35"/>
+        <v>4</v>
+      </c>
+      <c r="T158" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X158" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y158" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z158" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA158" s="5">
+        <v>2</v>
+      </c>
+      <c r="AB158" s="5">
+        <v>8</v>
+      </c>
+      <c r="AC158" s="5">
+        <v>2</v>
+      </c>
+      <c r="AJ158" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>4 doors</v>
+      </c>
     </row>
     <row r="159" spans="1:43">
-      <c r="P159" s="6"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="6"/>
+      <c r="A159" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B159" t="s">
+        <v>265</v>
+      </c>
+      <c r="C159">
+        <v>3</v>
+      </c>
+      <c r="E159" t="s">
+        <v>87</v>
+      </c>
+      <c r="G159" s="5">
+        <v>2003</v>
+      </c>
+      <c r="H159" s="5">
+        <v>20</v>
+      </c>
+      <c r="I159" s="5">
+        <v>25</v>
+      </c>
+      <c r="J159" s="5">
+        <v>20</v>
+      </c>
+      <c r="K159" s="5">
+        <v>14</v>
+      </c>
+      <c r="L159" s="5">
+        <v>14</v>
+      </c>
+      <c r="M159" s="5">
+        <v>14</v>
+      </c>
+      <c r="P159" s="6">
+        <f t="shared" si="33"/>
+        <v>42</v>
+      </c>
+      <c r="Q159" s="6">
+        <f t="shared" si="34"/>
+        <v>3</v>
+      </c>
+      <c r="R159" s="6">
+        <f t="shared" si="35"/>
+        <v>3</v>
+      </c>
+      <c r="T159" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X159" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y159" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z159" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA159" s="5">
+        <v>2</v>
+      </c>
+      <c r="AB159" s="5">
+        <v>8</v>
+      </c>
+      <c r="AC159" s="5">
+        <v>2</v>
+      </c>
+      <c r="AJ159" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>3 doors</v>
+      </c>
     </row>
     <row r="160" spans="1:43">
-      <c r="P160" s="6"/>
-      <c r="Q160" s="6"/>
-      <c r="R160" s="6"/>
-    </row>
-    <row r="161" spans="16:18">
-      <c r="P161" s="6"/>
-      <c r="Q161" s="6"/>
-      <c r="R161" s="6"/>
-    </row>
-    <row r="162" spans="16:18">
-      <c r="P162" s="6"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="6"/>
-    </row>
-    <row r="163" spans="16:18">
+      <c r="A160" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="B160" t="s">
+        <v>72</v>
+      </c>
+      <c r="C160">
+        <v>3</v>
+      </c>
+      <c r="E160" t="s">
+        <v>87</v>
+      </c>
+      <c r="H160" s="5">
+        <v>20</v>
+      </c>
+      <c r="I160" s="5">
+        <v>25</v>
+      </c>
+      <c r="J160" s="5">
+        <v>20</v>
+      </c>
+      <c r="K160" s="5">
+        <v>14</v>
+      </c>
+      <c r="L160" s="5">
+        <v>14</v>
+      </c>
+      <c r="M160" s="5">
+        <v>14</v>
+      </c>
+      <c r="P160" s="6">
+        <f t="shared" si="33"/>
+        <v>42</v>
+      </c>
+      <c r="Q160" s="6">
+        <f t="shared" si="34"/>
+        <v>9</v>
+      </c>
+      <c r="R160" s="6">
+        <f t="shared" si="35"/>
+        <v>4.7733333333333334</v>
+      </c>
+      <c r="T160" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="V160" s="5">
+        <v>12</v>
+      </c>
+      <c r="W160" s="5">
+        <v>86</v>
+      </c>
+      <c r="X160" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y160" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z160" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA160" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ160" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>3 doors</v>
+      </c>
+    </row>
+    <row r="161" spans="1:36">
+      <c r="A161" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="B161" t="s">
+        <v>72</v>
+      </c>
+      <c r="C161">
+        <v>2</v>
+      </c>
+      <c r="E161" t="s">
+        <v>87</v>
+      </c>
+      <c r="H161" s="5">
+        <v>20</v>
+      </c>
+      <c r="I161" s="5">
+        <v>25</v>
+      </c>
+      <c r="J161" s="5">
+        <v>20</v>
+      </c>
+      <c r="K161" s="5">
+        <v>14</v>
+      </c>
+      <c r="L161" s="5">
+        <v>14</v>
+      </c>
+      <c r="P161" s="6">
+        <f t="shared" si="33"/>
+        <v>28</v>
+      </c>
+      <c r="Q161" s="6">
+        <f t="shared" si="34"/>
+        <v>8</v>
+      </c>
+      <c r="R161" s="6">
+        <f t="shared" si="35"/>
+        <v>3.7733333333333334</v>
+      </c>
+      <c r="T161" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="V161" s="5">
+        <v>12</v>
+      </c>
+      <c r="W161" s="5">
+        <v>86</v>
+      </c>
+      <c r="X161" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y161" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z161" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA161" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ161" s="4" t="str">
+        <f t="shared" ref="AJ161" si="36">C161 &amp; " doors"</f>
+        <v>2 doors</v>
+      </c>
+    </row>
+    <row r="162" spans="1:36">
+      <c r="A162" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B162" t="s">
+        <v>72</v>
+      </c>
+      <c r="C162">
+        <v>3</v>
+      </c>
+      <c r="E162" t="s">
+        <v>87</v>
+      </c>
+      <c r="H162" s="5">
+        <v>20</v>
+      </c>
+      <c r="I162" s="5">
+        <v>25</v>
+      </c>
+      <c r="J162" s="5">
+        <v>20</v>
+      </c>
+      <c r="K162" s="5">
+        <v>14</v>
+      </c>
+      <c r="L162" s="5">
+        <v>14</v>
+      </c>
+      <c r="M162" s="5">
+        <v>14</v>
+      </c>
+      <c r="P162" s="6">
+        <f t="shared" si="33"/>
+        <v>42</v>
+      </c>
+      <c r="Q162" s="6">
+        <f t="shared" si="34"/>
+        <v>9</v>
+      </c>
+      <c r="R162" s="6">
+        <f t="shared" si="35"/>
+        <v>4.7733333333333334</v>
+      </c>
+      <c r="T162" s="7">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="V162" s="5">
+        <v>12</v>
+      </c>
+      <c r="W162" s="5">
+        <v>86</v>
+      </c>
+      <c r="X162" s="5">
+        <v>185</v>
+      </c>
+      <c r="Y162" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z162" s="5">
+        <v>8</v>
+      </c>
+      <c r="AA162" s="5">
+        <v>5</v>
+      </c>
+      <c r="AJ162" s="4" t="str">
+        <f t="shared" si="31"/>
+        <v>3 doors</v>
+      </c>
+    </row>
+    <row r="163" spans="1:36">
       <c r="P163" s="6"/>
       <c r="Q163" s="6"/>
       <c r="R163" s="6"/>
     </row>
-    <row r="164" spans="16:18">
+    <row r="164" spans="1:36">
       <c r="P164" s="6"/>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
     </row>
-    <row r="165" spans="16:18">
+    <row r="165" spans="1:36">
       <c r="P165" s="6"/>
       <c r="Q165" s="6"/>
       <c r="R165" s="6"/>
     </row>
-    <row r="166" spans="16:18">
+    <row r="166" spans="1:36">
       <c r="P166" s="6"/>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
     </row>
-    <row r="167" spans="16:18">
+    <row r="167" spans="1:36">
       <c r="P167" s="6"/>
       <c r="Q167" s="6"/>
       <c r="R167" s="6"/>
     </row>
-    <row r="168" spans="16:18">
+    <row r="168" spans="1:36">
       <c r="P168" s="6"/>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
     </row>
-    <row r="169" spans="16:18">
+    <row r="169" spans="1:36">
       <c r="P169" s="6"/>
       <c r="Q169" s="6"/>
       <c r="R169" s="6"/>
     </row>
-    <row r="170" spans="16:18">
+    <row r="170" spans="1:36">
       <c r="P170" s="6"/>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
     </row>
-    <row r="171" spans="16:18">
+    <row r="171" spans="1:36">
       <c r="P171" s="6"/>
       <c r="Q171" s="6"/>
       <c r="R171" s="6"/>
+    </row>
+    <row r="172" spans="1:36">
+      <c r="P172" s="6"/>
+      <c r="Q172" s="6"/>
+      <c r="R172" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AQ148" xr:uid="{4632EB64-3C9B-49A1-A2BE-C39B89F1FE5D}">
